--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260922.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260922.xlsx
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>8,155,000</t>
+          <t>1,323,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,323,000</t>
+          <t>8,155,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>21,718,000</t>
+          <t>16,273,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2206</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>三陽工業</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>17,752,000</t>
+          <t>16,031,073</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>華航</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>16,273,000</t>
+          <t>55,082,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>16,031,073</t>
+          <t>21,718,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>華航</t>
+          <t>三陽工業</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>55,082,000</t>
+          <t>17,752,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
